--- a/result/LOOCV/SVR/without_41/nBA/1&2_nBA_SVR_LOOCV_mechanism_oriented_perc=90_without_41.xlsx
+++ b/result/LOOCV/SVR/without_41/nBA/1&2_nBA_SVR_LOOCV_mechanism_oriented_perc=90_without_41.xlsx
@@ -468,10 +468,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7531096914161661</v>
+        <v>0.4596231398115453</v>
       </c>
       <c r="C3" t="n">
-        <v>1.802470136072624</v>
+        <v>1.698899393828432</v>
       </c>
       <c r="D3" t="n">
         <v>1.8</v>
@@ -503,7 +503,7 @@
         <v>0.9622768900684014</v>
       </c>
       <c r="C5" t="n">
-        <v>1.895323295779975</v>
+        <v>1.895323295779974</v>
       </c>
       <c r="D5" t="n">
         <v>1.9</v>
@@ -516,10 +516,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.93928609533087</v>
+        <v>0.7935696953450355</v>
       </c>
       <c r="C6" t="n">
-        <v>2.28094729631602</v>
+        <v>1.950667995003196</v>
       </c>
       <c r="D6" t="n">
         <v>1.75</v>
@@ -532,10 +532,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7525510796645637</v>
+        <v>0.4127999183217883</v>
       </c>
       <c r="C7" t="n">
-        <v>1.585867521497822</v>
+        <v>1.679362087964434</v>
       </c>
       <c r="D7" t="n">
         <v>1.44</v>
@@ -580,10 +580,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.9109181179454033</v>
+        <v>0.829951153294366</v>
       </c>
       <c r="C10" t="n">
-        <v>1.700453988959739</v>
+        <v>1.731583141185818</v>
       </c>
       <c r="D10" t="n">
         <v>1.75</v>
@@ -628,10 +628,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.7439922004779003</v>
+        <v>0.4003954424824433</v>
       </c>
       <c r="C13" t="n">
-        <v>1.53792708969103</v>
+        <v>1.683877766354381</v>
       </c>
       <c r="D13" t="n">
         <v>1.45</v>
@@ -660,10 +660,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.4224090954328504</v>
+        <v>0.7879143668019706</v>
       </c>
       <c r="C15" t="n">
-        <v>1.77754048434547</v>
+        <v>1.801500193979754</v>
       </c>
       <c r="D15" t="n">
         <v>1.5</v>
@@ -708,7 +708,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.7593151492380799</v>
+        <v>0.7593151492380797</v>
       </c>
       <c r="C18" t="n">
         <v>2.783612351934546</v>
